--- a/reference/HF4-card-data.xlsx
+++ b/reference/HF4-card-data.xlsx
@@ -7513,7 +7513,7 @@
       <c r="J3" s="44" t="b">
         <v>0</v>
       </c>
-      <c r="K3" t="b">
+      <c r="K3" s="0" t="b">
         <v>0</v>
       </c>
       <c r="L3" s="31" t="b">
@@ -7556,7 +7556,7 @@
       <c r="J4" s="44" t="b">
         <v>0</v>
       </c>
-      <c r="K4" t="b">
+      <c r="K4" s="0" t="b">
         <v>0</v>
       </c>
       <c r="L4" s="31" t="b">
@@ -7605,7 +7605,7 @@
       <c r="J5" s="44" t="b">
         <v>0</v>
       </c>
-      <c r="K5" t="b">
+      <c r="K5" s="0" t="b">
         <v>1</v>
       </c>
       <c r="L5" s="31" t="b">
@@ -7648,7 +7648,7 @@
       <c r="J6" s="44" t="b">
         <v>0</v>
       </c>
-      <c r="K6" t="b">
+      <c r="K6" s="0" t="b">
         <v>0</v>
       </c>
       <c r="L6" s="31" t="b">
@@ -7697,7 +7697,7 @@
       <c r="J7" s="44" t="b">
         <v>0</v>
       </c>
-      <c r="K7" t="b">
+      <c r="K7" s="0" t="b">
         <v>0</v>
       </c>
       <c r="L7" s="31" t="b">
@@ -7742,7 +7742,7 @@
       <c r="J8" s="44" t="b">
         <v>0</v>
       </c>
-      <c r="K8" t="b">
+      <c r="K8" s="0" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="31" t="b">
@@ -7791,7 +7791,7 @@
       <c r="J9" s="44" t="b">
         <v>0</v>
       </c>
-      <c r="K9" t="b">
+      <c r="K9" s="0" t="b">
         <v>0</v>
       </c>
       <c r="L9" s="31" t="b">
@@ -7834,7 +7834,7 @@
       <c r="J10" s="44" t="b">
         <v>0</v>
       </c>
-      <c r="K10" t="b">
+      <c r="K10" s="0" t="b">
         <v>0</v>
       </c>
       <c r="L10" s="31" t="b">
@@ -7881,7 +7881,7 @@
       <c r="J11" s="44" t="b">
         <v>0</v>
       </c>
-      <c r="K11" t="b">
+      <c r="K11" s="0" t="b">
         <v>0</v>
       </c>
       <c r="L11" s="31" t="b">
@@ -7924,7 +7924,7 @@
       <c r="J12" s="44" t="b">
         <v>0</v>
       </c>
-      <c r="K12" t="b">
+      <c r="K12" s="0" t="b">
         <v>0</v>
       </c>
       <c r="L12" s="31" t="b">
@@ -7973,7 +7973,7 @@
       <c r="J13" s="44" t="b">
         <v>0</v>
       </c>
-      <c r="K13" t="b">
+      <c r="K13" s="0" t="b">
         <v>0</v>
       </c>
       <c r="L13" s="31" t="b">
@@ -8018,7 +8018,7 @@
       <c r="J14" s="44" t="b">
         <v>0</v>
       </c>
-      <c r="K14" t="b">
+      <c r="K14" s="0" t="b">
         <v>0</v>
       </c>
       <c r="L14" s="31" t="b">
@@ -8067,7 +8067,7 @@
       <c r="J15" s="47" t="b">
         <v>1</v>
       </c>
-      <c r="K15" t="b">
+      <c r="K15" s="0" t="b">
         <v>0</v>
       </c>
       <c r="L15" s="31" t="b">
@@ -8109,7 +8109,7 @@
       <c r="J16" s="47" t="b">
         <v>0</v>
       </c>
-      <c r="K16" t="b">
+      <c r="K16" s="0" t="b">
         <v>0</v>
       </c>
       <c r="L16" s="31" t="b">
@@ -8160,7 +8160,7 @@
       <c r="J17" s="47" t="b">
         <v>0</v>
       </c>
-      <c r="K17" t="b">
+      <c r="K17" s="0" t="b">
         <v>0</v>
       </c>
       <c r="L17" s="31" t="b">
@@ -8205,7 +8205,7 @@
       <c r="J18" s="44" t="b">
         <v>0</v>
       </c>
-      <c r="K18" t="b">
+      <c r="K18" s="0" t="b">
         <v>0</v>
       </c>
       <c r="L18" s="31" t="b">
@@ -8249,7 +8249,7 @@
       <c r="J19" s="47" t="b">
         <v>0</v>
       </c>
-      <c r="K19" t="b">
+      <c r="K19" s="0" t="b">
         <v>0</v>
       </c>
       <c r="L19" s="31" t="b">
@@ -8292,7 +8292,7 @@
       <c r="J20" s="44" t="b">
         <v>0</v>
       </c>
-      <c r="K20" t="b">
+      <c r="K20" s="0" t="b">
         <v>0</v>
       </c>
       <c r="L20" s="31" t="b">
@@ -8341,7 +8341,7 @@
       <c r="J21" s="47" t="b">
         <v>0</v>
       </c>
-      <c r="K21" t="b">
+      <c r="K21" s="0" t="b">
         <v>0</v>
       </c>
       <c r="L21" s="31" t="b">
@@ -8386,7 +8386,7 @@
       <c r="J22" s="44" t="b">
         <v>0</v>
       </c>
-      <c r="K22" t="b">
+      <c r="K22" s="0" t="b">
         <v>0</v>
       </c>
       <c r="L22" s="31" t="b">
@@ -8439,7 +8439,7 @@
       <c r="J23" s="44" t="b">
         <v>0</v>
       </c>
-      <c r="K23" t="b">
+      <c r="K23" s="0" t="b">
         <v>0</v>
       </c>
       <c r="L23" s="31" t="b">
@@ -8484,7 +8484,7 @@
       <c r="J24" s="44" t="b">
         <v>0</v>
       </c>
-      <c r="K24" t="b">
+      <c r="K24" s="0" t="b">
         <v>0</v>
       </c>
       <c r="L24" s="31" t="b">
@@ -8533,7 +8533,7 @@
       <c r="J25" s="47" t="b">
         <v>0</v>
       </c>
-      <c r="K25" t="b">
+      <c r="K25" s="0" t="b">
         <v>0</v>
       </c>
       <c r="L25" s="31" t="b">
@@ -8578,7 +8578,7 @@
       <c r="J26" s="48" t="b">
         <v>0</v>
       </c>
-      <c r="K26" t="b">
+      <c r="K26" s="0" t="b">
         <v>0</v>
       </c>
       <c r="L26" s="58" t="b">
@@ -12943,7 +12943,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="24.38" customWidth="1" style="91" min="1" max="1"/>
@@ -12971,14 +12971,15 @@
         </is>
       </c>
       <c r="G1" s="93" t="n"/>
-      <c r="H1" s="94" t="n"/>
-      <c r="I1" s="51" t="inlineStr">
+      <c r="H1" s="93" t="n"/>
+      <c r="I1" s="94" t="n"/>
+      <c r="J1" s="51" t="inlineStr">
         <is>
           <t>Support Requirements</t>
         </is>
       </c>
-      <c r="J1" s="94" t="n"/>
-      <c r="K1" s="70" t="n"/>
+      <c r="K1" s="94" t="n"/>
+      <c r="L1" s="70" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -13018,22 +13019,27 @@
 Consumption</t>
         </is>
       </c>
-      <c r="H2" s="87" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Fuel Type</t>
+        </is>
+      </c>
+      <c r="I2" s="87" t="inlineStr">
         <is>
           <t>Powersat</t>
         </is>
       </c>
-      <c r="I2" s="12" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>e Generator</t>
         </is>
       </c>
-      <c r="J2" s="11" t="inlineStr">
+      <c r="K2" s="11" t="inlineStr">
         <is>
           <t>Therms</t>
         </is>
       </c>
-      <c r="K2" s="14" t="inlineStr">
+      <c r="L2" s="14" t="inlineStr">
         <is>
           <t>Ability</t>
         </is>
@@ -13067,16 +13073,21 @@
       <c r="G3" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H3" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J3" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="23" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Dirt</t>
+        </is>
+      </c>
+      <c r="I3" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="23" t="inlineStr">
         <is>
           <t>HOME: Boost direct to Home Bernal without doubling boost costs.</t>
         </is>
@@ -13105,16 +13116,21 @@
       <c r="G4" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H4" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J4" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="23" t="inlineStr">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Dirt</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="23" t="inlineStr">
         <is>
           <t>Your factory-assisted landings/liftoffs anywhere treat lander burns as normal Burn Spaces.</t>
         </is>
@@ -13148,16 +13164,21 @@
       <c r="G5" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H5" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="23" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Dirt</t>
+        </is>
+      </c>
+      <c r="I5" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="23" t="inlineStr">
         <is>
           <t>HOME: You are always the 1st player, superseding all other claimants.</t>
         </is>
@@ -13186,16 +13207,21 @@
       <c r="G6" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="88" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Dirt</t>
+        </is>
+      </c>
+      <c r="I6" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="88" t="inlineStr">
         <is>
           <t>+2 VP per Dirtside for this Bernal.</t>
         </is>
@@ -13229,16 +13255,21 @@
       <c r="G7" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H7" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="23" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Dirt</t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t>HOME: Gain the Powersat faction privilege.</t>
         </is>
@@ -13267,16 +13298,21 @@
       <c r="G8" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H8" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="23" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Dirt</t>
+        </is>
+      </c>
+      <c r="I8" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="23" t="inlineStr">
         <is>
           <t>Gain the Powersat faction privilege. Powersat push includes a Bonus Pivot.</t>
         </is>
@@ -13310,16 +13346,21 @@
       <c r="G9" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="23" t="inlineStr">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Dirt</t>
+        </is>
+      </c>
+      <c r="I9" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="23" t="inlineStr">
         <is>
           <t>HOME: Boost direct to Home Bernal without doubling boost costs.</t>
         </is>
@@ -13348,16 +13389,21 @@
       <c r="G10" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="23" t="inlineStr">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Dirt</t>
+        </is>
+      </c>
+      <c r="I10" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="23" t="inlineStr">
         <is>
           <t>Your factory-assisted landings/liftoffs anywhere treat lander burns as normal Burn Spaces.</t>
         </is>
@@ -13391,16 +13437,21 @@
       <c r="G11" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" s="23" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Dirt</t>
+        </is>
+      </c>
+      <c r="I11" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" s="23" t="inlineStr">
         <is>
           <t>HOME: Your Crew has an On-Board Nuclear X reactor.</t>
         </is>
@@ -13429,16 +13480,21 @@
       <c r="G12" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I12" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J12" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" s="23" t="inlineStr">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Dirt</t>
+        </is>
+      </c>
+      <c r="I12" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" s="23" t="inlineStr">
         <is>
           <t>Your Crew has an On-Board Nuclear "ANY" reactor.</t>
         </is>
@@ -13472,16 +13528,21 @@
       <c r="G13" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I13" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J13" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="23" t="inlineStr">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Dirt</t>
+        </is>
+      </c>
+      <c r="I13" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="23" t="inlineStr">
         <is>
           <t>HOME: Gain the Skunkworks faction privilege.</t>
         </is>
@@ -13510,16 +13571,21 @@
       <c r="G14" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H14" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I14" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="23" t="inlineStr">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Dirt</t>
+        </is>
+      </c>
+      <c r="I14" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="23" t="inlineStr">
         <is>
           <t>Gain the Skunkworks faction privilege &amp; impose academia hand limit on all opponents.</t>
         </is>
@@ -13553,16 +13619,21 @@
       <c r="G15" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I15" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="23" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Dirt</t>
+        </is>
+      </c>
+      <c r="I15" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="23" t="inlineStr">
         <is>
           <t>HOME: +1 to the Net Thrust of your Spacecraft that use Solar-Power.</t>
         </is>
@@ -13591,16 +13662,21 @@
       <c r="G16" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H16" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J16" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="88" t="inlineStr">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Dirt</t>
+        </is>
+      </c>
+      <c r="I16" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="88" t="inlineStr">
         <is>
           <t>+2 to the Net Thrust of your Spacecraft that use Solar-Power.</t>
         </is>
@@ -13634,16 +13710,21 @@
       <c r="G17" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H17" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I17" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="23" t="inlineStr">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Dirt</t>
+        </is>
+      </c>
+      <c r="I17" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="23" t="inlineStr">
         <is>
           <t>HOME: You are immune to budget cuts.</t>
         </is>
@@ -13672,16 +13753,21 @@
       <c r="G18" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H18" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="23" t="inlineStr">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Dirt</t>
+        </is>
+      </c>
+      <c r="I18" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="23" t="inlineStr">
         <is>
           <t>Gain +1 Token VP for each Colony Dome. Your Crew and Human Colonists have a rad-hard of at least 7.</t>
         </is>
@@ -13715,16 +13801,21 @@
       <c r="G19" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H19" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I19" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="23" t="inlineStr">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Dirt</t>
+        </is>
+      </c>
+      <c r="I19" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="23" t="inlineStr">
         <is>
           <t>HOME: (Module 0) Your delegates in the Ideology of your Faction color are +1 VP each.</t>
         </is>
@@ -13753,16 +13844,21 @@
       <c r="G20" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H20" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I20" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="23" t="inlineStr">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Dirt</t>
+        </is>
+      </c>
+      <c r="I20" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="23" t="inlineStr">
         <is>
           <t>(Module 0) Your delegates in the assembly are +1 VP each.</t>
         </is>
@@ -13796,16 +13892,21 @@
       <c r="G21" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H21" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I21" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="23" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Dirt</t>
+        </is>
+      </c>
+      <c r="I21" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="23" t="inlineStr">
         <is>
           <t>HOME: Can designate any Spacecraft to forgo Belt Rolls in the Radiation Belts near Earth.</t>
         </is>
@@ -13835,16 +13936,21 @@
       <c r="G22" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="H22" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="I22" s="58" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="89" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Dirt</t>
+        </is>
+      </c>
+      <c r="I22" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" s="58" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="89" t="inlineStr">
         <is>
           <t>+2 VP per Dirtside for this Bernal.</t>
         </is>
@@ -13853,17 +13959,17 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="C9:C10"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="C3:C4"/>
     <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C7:C8"/>
     <mergeCell ref="C21:C22"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="C19:C20"/>
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="C11:C12"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="I1:J1"/>
     <mergeCell ref="C5:C6"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="C19:C20"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:A22">
     <cfRule type="expression" priority="1" dxfId="0">

--- a/reference/HF4-card-data.xlsx
+++ b/reference/HF4-card-data.xlsx
@@ -4284,24 +4284,24 @@
       </c>
       <c r="I31" s="31" t="n"/>
       <c r="M31" s="45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" s="45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" s="45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P31" s="19" t="n"/>
       <c r="Q31" s="31" t="n"/>
       <c r="R31" s="45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" s="45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T31" s="19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U31" s="31" t="b">
         <v>0</v>
@@ -4330,24 +4330,24 @@
       </c>
       <c r="I32" s="31" t="n"/>
       <c r="M32" s="45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" s="45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" s="45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" s="19" t="n"/>
       <c r="Q32" s="31" t="n"/>
       <c r="R32" s="45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" s="45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T32" s="19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U32" s="31" t="b">
         <v>0</v>
@@ -13019,7 +13019,7 @@
 Consumption</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="0" t="inlineStr">
         <is>
           <t>Fuel Type</t>
         </is>
@@ -13073,7 +13073,7 @@
       <c r="G3" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="0" t="inlineStr">
         <is>
           <t>Dirt</t>
         </is>
@@ -13116,7 +13116,7 @@
       <c r="G4" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="0" t="inlineStr">
         <is>
           <t>Dirt</t>
         </is>
@@ -13164,7 +13164,7 @@
       <c r="G5" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="0" t="inlineStr">
         <is>
           <t>Dirt</t>
         </is>
@@ -13207,7 +13207,7 @@
       <c r="G6" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="0" t="inlineStr">
         <is>
           <t>Dirt</t>
         </is>
@@ -13255,7 +13255,7 @@
       <c r="G7" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="0" t="inlineStr">
         <is>
           <t>Dirt</t>
         </is>
@@ -13298,7 +13298,7 @@
       <c r="G8" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="0" t="inlineStr">
         <is>
           <t>Dirt</t>
         </is>
@@ -13346,7 +13346,7 @@
       <c r="G9" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="0" t="inlineStr">
         <is>
           <t>Dirt</t>
         </is>
@@ -13389,7 +13389,7 @@
       <c r="G10" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="0" t="inlineStr">
         <is>
           <t>Dirt</t>
         </is>
@@ -13437,7 +13437,7 @@
       <c r="G11" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="0" t="inlineStr">
         <is>
           <t>Dirt</t>
         </is>
@@ -13480,7 +13480,7 @@
       <c r="G12" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="0" t="inlineStr">
         <is>
           <t>Dirt</t>
         </is>
@@ -13528,7 +13528,7 @@
       <c r="G13" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="0" t="inlineStr">
         <is>
           <t>Dirt</t>
         </is>
@@ -13571,7 +13571,7 @@
       <c r="G14" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="0" t="inlineStr">
         <is>
           <t>Dirt</t>
         </is>
@@ -13619,7 +13619,7 @@
       <c r="G15" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="0" t="inlineStr">
         <is>
           <t>Dirt</t>
         </is>
@@ -13662,7 +13662,7 @@
       <c r="G16" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="0" t="inlineStr">
         <is>
           <t>Dirt</t>
         </is>
@@ -13710,7 +13710,7 @@
       <c r="G17" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="0" t="inlineStr">
         <is>
           <t>Dirt</t>
         </is>
@@ -13753,7 +13753,7 @@
       <c r="G18" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="0" t="inlineStr">
         <is>
           <t>Dirt</t>
         </is>
@@ -13801,7 +13801,7 @@
       <c r="G19" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="0" t="inlineStr">
         <is>
           <t>Dirt</t>
         </is>
@@ -13844,7 +13844,7 @@
       <c r="G20" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="0" t="inlineStr">
         <is>
           <t>Dirt</t>
         </is>
@@ -13892,7 +13892,7 @@
       <c r="G21" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="0" t="inlineStr">
         <is>
           <t>Dirt</t>
         </is>
@@ -13936,7 +13936,7 @@
       <c r="G22" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="0" t="inlineStr">
         <is>
           <t>Dirt</t>
         </is>
@@ -13962,14 +13962,14 @@
     <mergeCell ref="F1:I1"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C13:C14"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="C21:C22"/>
+    <mergeCell ref="J1:K1"/>
     <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C19:C20"/>
     <mergeCell ref="C11:C12"/>
+    <mergeCell ref="C13:C14"/>
     <mergeCell ref="C5:C6"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="C19:C20"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:A22">
     <cfRule type="expression" priority="1" dxfId="0">

--- a/reference/HF4-card-data.xlsx
+++ b/reference/HF4-card-data.xlsx
@@ -4581,9 +4581,7 @@
         <v>5</v>
       </c>
       <c r="I36" s="31" t="n"/>
-      <c r="M36" s="45" t="b">
-        <v>1</v>
-      </c>
+      <c r="M36" s="45" t="n"/>
       <c r="N36" s="45" t="b">
         <v>0</v>
       </c>
